--- a/c4ai_publicacoes.xlsx
+++ b/c4ai_publicacoes.xlsx
@@ -1674,7 +1674,9 @@
           <t>AGRIBIO</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>2021</v>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
           <t>Learning to sense from events via semantic variational autoencoder</t>
